--- a/ZonasEscolares/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/ZonasEscolares/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/ZonasEscolares/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>302 RUSO</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-9.07639</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-78.58864</v>
-      </c>
-      <c r="I2" t="n">
-        <v>468</v>
-      </c>
-      <c r="J2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-9.07639</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-78.58864</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>313</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-9.09037</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.5685</v>
-      </c>
-      <c r="I3" t="n">
-        <v>224</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-9.09037</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.5685</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>316 NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-9.07039</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-78.59414</v>
-      </c>
-      <c r="I4" t="n">
-        <v>254</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-9.07039</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-78.59414</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>1535 LA HUACA TESORO DE LOS NIÑOS</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-9.051292999999999</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-78.58774200000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>239</v>
-      </c>
-      <c r="J5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-9.051293</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-78.587742</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>1542 CAPULLITOS DE AMOR</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-9.05762</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-78.58641</v>
-      </c>
-      <c r="I6" t="n">
-        <v>404</v>
-      </c>
-      <c r="J6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-9.05762</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-78.58641</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>1546</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-9.073270000000001</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-78.57635999999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>200</v>
-      </c>
-      <c r="J7" t="n">
-        <v>9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-9.07327</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-78.57636</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>88232 NUESTRA VIRGEN MARIA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-9.077400000000001</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.58078999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>519</v>
-      </c>
-      <c r="J8" t="n">
-        <v>24</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-9.0774</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.58079</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>89013</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-9.071910000000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-78.58342</v>
-      </c>
-      <c r="I9" t="n">
-        <v>254</v>
-      </c>
-      <c r="J9" t="n">
-        <v>18</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-9.07191</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-78.58342</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>88001</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-9.074149999999999</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-78.59419</v>
-      </c>
-      <c r="I10" t="n">
-        <v>728</v>
-      </c>
-      <c r="J10" t="n">
-        <v>32</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-9.07415</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-78.59419</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>88005 CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-9.077920000000001</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-78.58883</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1109</v>
-      </c>
-      <c r="J11" t="n">
-        <v>48</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-9.07792</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-78.58883</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>88008 MANUEL PERALTA HURTADO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-9.088900000000001</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-78.57471</v>
-      </c>
-      <c r="I12" t="n">
-        <v>280</v>
-      </c>
-      <c r="J12" t="n">
-        <v>18</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-9.0889</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-78.57471</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>88009 ENRIQUE MEIGGS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-9.093249999999999</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-78.5699</v>
-      </c>
-      <c r="I13" t="n">
-        <v>537</v>
-      </c>
-      <c r="J13" t="n">
-        <v>23</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-9.09325</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-78.5699</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>88011 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-9.103114</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-78.565121</v>
-      </c>
-      <c r="I14" t="n">
-        <v>282</v>
-      </c>
-      <c r="J14" t="n">
-        <v>19</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-9.103114</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-78.565121</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>88012</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-9.07921</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-78.57726</v>
-      </c>
-      <c r="I15" t="n">
-        <v>362</v>
-      </c>
-      <c r="J15" t="n">
-        <v>18</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-9.07921</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-78.57726</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>88013 ELEAZAR GUZMAN BARRON</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-9.073980000000001</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-78.57539</v>
-      </c>
-      <c r="I16" t="n">
-        <v>687</v>
-      </c>
-      <c r="J16" t="n">
-        <v>43</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-9.07398</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-78.57539</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>88014 JOSE OLAYA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-9.085229999999999</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-78.56895</v>
-      </c>
-      <c r="I17" t="n">
-        <v>910</v>
-      </c>
-      <c r="J17" t="n">
-        <v>56</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-9.08523</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-78.56895</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>88015 EDITH WEED DAVIS</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-9.075369999999999</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-78.57189</v>
-      </c>
-      <c r="I18" t="n">
-        <v>516</v>
-      </c>
-      <c r="J18" t="n">
-        <v>33</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-9.07537</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-78.57189</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>88016 JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-9.06955</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-78.57680000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>603</v>
-      </c>
-      <c r="J19" t="n">
-        <v>35</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-9.06955</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-78.5768</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>88020 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-9.06101</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-78.58129</v>
-      </c>
-      <c r="I20" t="n">
-        <v>404</v>
-      </c>
-      <c r="J20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-9.06101</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-78.58129</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>88031 REPUBLICA PERUANA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-9.060040000000001</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-78.58588</v>
-      </c>
-      <c r="I21" t="n">
-        <v>514</v>
-      </c>
-      <c r="J21" t="n">
-        <v>38</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-9.06004</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-78.58588</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>88032 APOSTOL SAN PEDRO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-9.045787000000001</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-78.591611</v>
-      </c>
-      <c r="I22" t="n">
-        <v>402</v>
-      </c>
-      <c r="J22" t="n">
-        <v>20</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-9.045787</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-78.591611</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>88034 PEDRO RUIZ GALLO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-9.057969999999999</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-78.58932</v>
-      </c>
-      <c r="I23" t="n">
-        <v>582</v>
-      </c>
-      <c r="J23" t="n">
-        <v>25</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-9.05797</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-78.58932</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>88036 MARIANO MELGAR</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-9.05161</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-78.58521</v>
-      </c>
-      <c r="I24" t="n">
-        <v>936</v>
-      </c>
-      <c r="J24" t="n">
-        <v>44</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-9.05161</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-78.58521</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>88037 ANTENOR SANCHEZ</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-9.052949999999999</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-78.57464</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1154</v>
-      </c>
-      <c r="J25" t="n">
-        <v>55</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-9.05295</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-78.57464</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1154</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>88046 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-8.997156</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-78.55548899999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>799</v>
-      </c>
-      <c r="J26" t="n">
-        <v>43</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-8.997156</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-78.555489</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>88072</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-9.056150000000001</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-78.57751</v>
-      </c>
-      <c r="I27" t="n">
-        <v>222</v>
-      </c>
-      <c r="J27" t="n">
-        <v>11</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-9.05615</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-78.57751</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>88183</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-8.946399</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-78.51763099999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>255</v>
-      </c>
-      <c r="J28" t="n">
-        <v>16</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-8.946399</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-78.517631</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>88226 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-9.075419999999999</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-78.57868999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>547</v>
-      </c>
-      <c r="J29" t="n">
-        <v>27</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-9.07542</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-78.57869</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>88229 SAN JUAN</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-9.08813</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-78.56885</v>
-      </c>
-      <c r="I30" t="n">
-        <v>752</v>
-      </c>
-      <c r="J30" t="n">
-        <v>35</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-9.08813</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-78.56885</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>88239 LEONCIO PRADO</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-9.081189999999999</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-78.57252</v>
-      </c>
-      <c r="I31" t="n">
-        <v>288</v>
-      </c>
-      <c r="J31" t="n">
-        <v>14</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-9.08119</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-78.57252</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>88357 TERESA GONZALES DE FANNING</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-9.046379999999999</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-78.58619</v>
-      </c>
-      <c r="I32" t="n">
-        <v>813</v>
-      </c>
-      <c r="J32" t="n">
-        <v>39</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-9.04638</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-78.58619</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>89001</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-9.07225</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-78.59538999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1010</v>
-      </c>
-      <c r="J33" t="n">
-        <v>39</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-9.07225</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-78.59539</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>89002</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-9.073219999999999</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-78.59575</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1743</v>
-      </c>
-      <c r="J34" t="n">
-        <v>88</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-9.07322</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-78.59575</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1743</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>89007</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-9.06772</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-78.58247</v>
-      </c>
-      <c r="I35" t="n">
-        <v>829</v>
-      </c>
-      <c r="J35" t="n">
-        <v>36</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-9.06772</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-78.58247</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>89008 ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-9.05274</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-78.582008</v>
-      </c>
-      <c r="I36" t="n">
-        <v>415</v>
-      </c>
-      <c r="J36" t="n">
-        <v>24</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-9.05274</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-78.582008</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>89009 8 DE OCTUBRE</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-9.064220000000001</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-78.58580000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>403</v>
-      </c>
-      <c r="J37" t="n">
-        <v>33</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-9.06422</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-78.5858</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>89011 ELIAS AGUIRRE ROMERO</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-9.071</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-78.58449</v>
-      </c>
-      <c r="I38" t="n">
-        <v>384</v>
-      </c>
-      <c r="J38" t="n">
-        <v>22</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-9.071</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-78.58449</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>INMACULADA DE LA MERCED</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-9.06845</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-78.59415</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1676</v>
-      </c>
-      <c r="J39" t="n">
-        <v>112</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-9.06845</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-78.59415</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>SAN PEDRO</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-9.081842999999999</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-78.58245100000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>871</v>
-      </c>
-      <c r="J40" t="n">
-        <v>47</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-9.081843</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-78.582451</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-9.071400000000001</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-78.59572</v>
-      </c>
-      <c r="I41" t="n">
-        <v>851</v>
-      </c>
-      <c r="J41" t="n">
-        <v>58</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-9.0714</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-78.59572</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>SANTA MARIA REINA</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-9.069100000000001</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-78.58308</v>
-      </c>
-      <c r="I42" t="n">
-        <v>628</v>
-      </c>
-      <c r="J42" t="n">
-        <v>42</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-9.0691</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-78.58308</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>LA LIBERTAD</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-9.09775</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-78.57053999999999</v>
-      </c>
-      <c r="I43" t="n">
-        <v>322</v>
-      </c>
-      <c r="J43" t="n">
-        <v>34</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-9.09775</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-78.57054</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-9.05796</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-78.57932</v>
-      </c>
-      <c r="I44" t="n">
-        <v>283</v>
-      </c>
-      <c r="J44" t="n">
-        <v>25</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-9.05796</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-78.57932</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>POLITECNICO NACIONAL DEL SANTA</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-9.0806</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-78.58156</v>
-      </c>
-      <c r="I45" t="n">
-        <v>446</v>
-      </c>
-      <c r="J45" t="n">
-        <v>46</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-9.0806</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-78.58156</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>SAN JOSE OBRERO</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-9.058389999999999</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-78.58659</v>
-      </c>
-      <c r="I46" t="n">
-        <v>515</v>
-      </c>
-      <c r="J46" t="n">
-        <v>29</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-9.05839</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-78.58659</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>EL SANTA</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-9.073365000000001</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-78.590283</v>
-      </c>
-      <c r="I47" t="n">
-        <v>210</v>
-      </c>
-      <c r="J47" t="n">
-        <v>19</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-9.073365</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-78.590283</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>SAN VICENTE DE PAUL</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-9.07277</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-78.59220999999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>217</v>
-      </c>
-      <c r="J48" t="n">
-        <v>10</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-9.07277</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-78.59221</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-9.073782</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-78.60151399999999</v>
-      </c>
-      <c r="I49" t="n">
-        <v>645</v>
-      </c>
-      <c r="J49" t="n">
-        <v>33</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-9.073782</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-78.601514</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-9.07366</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-78.59421</v>
-      </c>
-      <c r="I50" t="n">
-        <v>431</v>
-      </c>
-      <c r="J50" t="n">
-        <v>18</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-9.07366</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-78.59421</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>FE Y ALEGRIA 16</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-9.092359999999999</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-78.56034</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1115</v>
-      </c>
-      <c r="J51" t="n">
-        <v>62</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-9.09236</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-78.56034</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>NIÑO DIOS</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-9.06499</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-78.58446000000001</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1059</v>
-      </c>
-      <c r="J52" t="n">
-        <v>50</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-9.06499</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-78.58446</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>ANTONIO RAIMONDI</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-9.07314</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-78.59392</v>
-      </c>
-      <c r="I53" t="n">
-        <v>668</v>
-      </c>
-      <c r="J53" t="n">
-        <v>42</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-9.07314</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-78.59392</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>88050</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-9.014075999999999</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-78.13864599999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>292</v>
-      </c>
-      <c r="J54" t="n">
-        <v>23</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-9.014076</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-78.138646</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>89506 EDUARDO FERRICK RING</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-9.022762</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-78.619569</v>
-      </c>
-      <c r="I55" t="n">
-        <v>568</v>
-      </c>
-      <c r="J55" t="n">
-        <v>25</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-9.022762</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-78.619569</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>88099</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-9.156067</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-78.327754</v>
-      </c>
-      <c r="I56" t="n">
-        <v>282</v>
-      </c>
-      <c r="J56" t="n">
-        <v>15</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-9.156067</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-78.327754</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>88049</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-8.908032</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-78.528023</v>
-      </c>
-      <c r="I57" t="n">
-        <v>902</v>
-      </c>
-      <c r="J57" t="n">
-        <v>54</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-8.908032</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-78.528023</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>88319 SANTA ROSA DE LIMA PATRONA DE AMERICA</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-8.967765</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-78.58311399999999</v>
-      </c>
-      <c r="I58" t="n">
-        <v>381</v>
-      </c>
-      <c r="J58" t="n">
-        <v>27</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-8.967765</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-78.583114</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>88330 SANTISIMA CRUZ DE MAYO</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-8.802923</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-78.552689</v>
-      </c>
-      <c r="I59" t="n">
-        <v>462</v>
-      </c>
-      <c r="J59" t="n">
-        <v>25</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-8.802923</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-78.552689</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>88331</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-8.894956000000002</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-78.565974</v>
-      </c>
-      <c r="I60" t="n">
-        <v>622</v>
-      </c>
-      <c r="J60" t="n">
-        <v>35</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-8.894956000000002</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-78.565974</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>88218</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-9.050538</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-78.521027</v>
-      </c>
-      <c r="I61" t="n">
-        <v>241</v>
-      </c>
-      <c r="J61" t="n">
-        <v>16</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-9.050538</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-78.521027</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>REAL PACIFICO</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-9.127022</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-78.524073</v>
-      </c>
-      <c r="I62" t="n">
-        <v>482</v>
-      </c>
-      <c r="J62" t="n">
-        <v>19</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-9.127022</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-78.524073</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>EL GRAN MAESTRO</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-9.11788</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-78.52169000000001</v>
-      </c>
-      <c r="I63" t="n">
-        <v>926</v>
-      </c>
-      <c r="J63" t="n">
-        <v>36</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-9.11788</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-78.52169</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>SAN FELIPE</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-9.151522</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-78.279124</v>
-      </c>
-      <c r="I64" t="n">
-        <v>259</v>
-      </c>
-      <c r="J64" t="n">
-        <v>19</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-9.151522</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-78.279124</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>MIS PRIMERAS HUELLITAS</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-9.06523</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-78.58508</v>
-      </c>
-      <c r="I65" t="n">
-        <v>202</v>
-      </c>
-      <c r="J65" t="n">
-        <v>17</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-9.06523</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-78.58508</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-9.074116999999999</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-78.60345700000001</v>
-      </c>
-      <c r="I66" t="n">
-        <v>389</v>
-      </c>
-      <c r="J66" t="n">
-        <v>26</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-9.074117</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-78.603457</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>EL SANTA</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-9.075480000000001</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-78.59544099999999</v>
-      </c>
-      <c r="I67" t="n">
-        <v>243</v>
-      </c>
-      <c r="J67" t="n">
-        <v>22</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-9.07548</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-78.595441</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-9.073539999999999</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-78.59463</v>
-      </c>
-      <c r="I68" t="n">
-        <v>401</v>
-      </c>
-      <c r="J68" t="n">
-        <v>16</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-9.07354</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-78.59463</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>BERESHIT</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-9.093831</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-78.55481399999999</v>
-      </c>
-      <c r="I69" t="n">
-        <v>226</v>
-      </c>
-      <c r="J69" t="n">
-        <v>24</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-9.093831</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-78.554814</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>HUMBOLDT KOLLEGIUM</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-9.081713000000001</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-78.57332</v>
-      </c>
-      <c r="I70" t="n">
-        <v>249</v>
-      </c>
-      <c r="J70" t="n">
-        <v>19</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-9.081713</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-78.57332</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/ZonasEscolares/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33802</t>
+          <t>33821</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>302 RUSO</t>
+          <t>313</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-9.07639</t>
+          <t>-9.09037</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.58864</t>
+          <t>-78.5685</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33821</t>
+          <t>33939</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>1535 LA HUACA TESORO DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.09037</t>
+          <t>-9.051293</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.5685</t>
+          <t>-78.587742</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33840</t>
+          <t>35170</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>316 NIÑO JESUS</t>
+          <t>SAN VICENTE DE PAUL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.07039</t>
+          <t>-9.07277</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.59414</t>
+          <t>-78.59221</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33939</t>
+          <t>34496</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1535 LA HUACA TESORO DE LOS NIÑOS</t>
+          <t>88072</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.051293</t>
+          <t>-9.05615</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.587742</t>
+          <t>-78.57751</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33963</t>
+          <t>34694</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1542 CAPULLITOS DE AMOR</t>
+          <t>INMACULADA DE LA MERCED</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.05762</t>
+          <t>-9.06845</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.58641</t>
+          <t>-78.59415</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>33840</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>316 NIÑO JESUS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.07327</t>
+          <t>-9.07039</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.57636</t>
+          <t>-78.59414</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34062</t>
+          <t>34552</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>88232 NUESTRA VIRGEN MARIA</t>
+          <t>88239 LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.0774</t>
+          <t>-9.08119</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.58079</t>
+          <t>-78.57252</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34104</t>
+          <t>33963</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>89013</t>
+          <t>1542 CAPULLITOS DE AMOR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.07191</t>
+          <t>-9.05762</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.58342</t>
+          <t>-78.58641</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>404</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>37051</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>88001</t>
+          <t>88099</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9.07415</t>
+          <t>-9.156067</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.59419</t>
+          <t>-78.327754</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34217</t>
+          <t>34514</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>88005 CORAZON DE JESUS</t>
+          <t>88183</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-9.07792</t>
+          <t>-8.946399</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.58883</t>
+          <t>-78.517631</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>34222</t>
+          <t>37918</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>88008 MANUEL PERALTA HURTADO</t>
+          <t>88218</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.0889</t>
+          <t>-9.050538</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.57471</t>
+          <t>-78.521027</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>241</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>637091</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>88009 ENRIQUE MEIGGS</t>
+          <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.09325</t>
+          <t>-9.07354</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.5699</t>
+          <t>-78.59463</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>401</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>34255</t>
+          <t>530453</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>88011 INCA GARCILASO DE LA VEGA</t>
+          <t>MIS PRIMERAS HUELLITAS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.103114</t>
+          <t>-9.06523</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.565121</t>
+          <t>-78.58508</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,27 +1307,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>34260</t>
+          <t>34104</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>88012</t>
+          <t>89013</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-9.07921</t>
+          <t>-9.07191</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-78.57726</t>
+          <t>-78.58342</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>34279</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>88013 ELEAZAR GUZMAN BARRON</t>
+          <t>88008 MANUEL PERALTA HURTADO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-9.07398</t>
+          <t>-9.0889</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-78.57539</t>
+          <t>-78.57471</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>34284</t>
+          <t>34260</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>88014 JOSE OLAYA</t>
+          <t>88012</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-9.08523</t>
+          <t>-9.07921</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.56895</t>
+          <t>-78.57726</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>34298</t>
+          <t>35245</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>88015 EDITH WEED DAVIS</t>
+          <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-9.07537</t>
+          <t>-9.07366</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.57189</t>
+          <t>-78.59421</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>431</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>34302</t>
+          <t>34255</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>88016 JOSE GALVEZ EGUSQUIZA</t>
+          <t>88011 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.06955</t>
+          <t>-9.103114</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.5768</t>
+          <t>-78.565121</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>35028</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>88020 VIRGEN DEL CARMEN</t>
+          <t>EL SANTA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-9.06101</t>
+          <t>-9.073365</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-78.58129</t>
+          <t>-78.590283</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>34383</t>
+          <t>38418</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>88031 REPUBLICA PERUANA</t>
+          <t>REAL PACIFICO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-9.06004</t>
+          <t>-9.127022</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.58588</t>
+          <t>-78.524073</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>482</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>34397</t>
+          <t>508193</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>88032 APOSTOL SAN PEDRO</t>
+          <t>SAN FELIPE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-9.045787</t>
+          <t>-9.151522</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-78.591611</t>
+          <t>-78.279124</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34401</t>
+          <t>864248</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>88034 PEDRO RUIZ GALLO</t>
+          <t>HUMBOLDT KOLLEGIUM</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-9.05797</t>
+          <t>-9.081713</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.58932</t>
+          <t>-78.57332</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>34415</t>
+          <t>33802</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>88036 MARIANO MELGAR</t>
+          <t>302 RUSO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-9.05161</t>
+          <t>-9.07639</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.58521</t>
+          <t>-78.58864</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>468</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34420</t>
+          <t>34397</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>88037 ANTENOR SANCHEZ</t>
+          <t>88032 APOSTOL SAN PEDRO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-9.05295</t>
+          <t>-9.045787</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-78.57464</t>
+          <t>-78.591611</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>402</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>34458</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>88046 JOSE CARLOS MARIATEGUI</t>
+          <t>89011 ELIAS AGUIRRE ROMERO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.997156</t>
+          <t>-9.071</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-78.555489</t>
+          <t>-78.58449</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>384</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>34496</t>
+          <t>627389</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>88072</t>
+          <t>EL SANTA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-9.05615</t>
+          <t>-9.07548</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-78.57751</t>
+          <t>-78.595441</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34514</t>
+          <t>34236</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>88183</t>
+          <t>88009 ENRIQUE MEIGGS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.946399</t>
+          <t>-9.09325</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-78.517631</t>
+          <t>-78.5699</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>537</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>34533</t>
+          <t>35957</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>88226 DANIEL ALCIDES CARRION</t>
+          <t>88050</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-9.07542</t>
+          <t>-9.014076</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.57869</t>
+          <t>-78.138646</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>292</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>34547</t>
+          <t>34062</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>88229 SAN JUAN</t>
+          <t>88232 NUESTRA VIRGEN MARIA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-9.08813</t>
+          <t>-9.0774</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.56885</t>
+          <t>-78.58079</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>519</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>34335</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>88239 LEONCIO PRADO</t>
+          <t>88020 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-9.08119</t>
+          <t>-9.06101</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.57252</t>
+          <t>-78.58129</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>404</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>34590</t>
+          <t>34665</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>88357 TERESA GONZALES DE FANNING</t>
+          <t>89008 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-9.04638</t>
+          <t>-9.05274</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.58619</t>
+          <t>-78.582008</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>415</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>34613</t>
+          <t>706089</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>89001</t>
+          <t>BERESHIT</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-9.07225</t>
+          <t>-9.093831</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-78.59539</t>
+          <t>-78.554814</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>34627</t>
+          <t>34401</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>89002</t>
+          <t>88034 PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-9.07322</t>
+          <t>-9.05797</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-78.59575</t>
+          <t>-78.58932</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>582</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>34651</t>
+          <t>34788</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>89007</t>
+          <t>MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-9.06772</t>
+          <t>-9.05796</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-78.58247</t>
+          <t>-78.57932</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>283</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>34665</t>
+          <t>36315</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>89008 ANDRES AVELINO CACERES</t>
+          <t>89506 EDUARDO FERRICK RING</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-9.05274</t>
+          <t>-9.022762</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-78.582008</t>
+          <t>-78.619569</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>568</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>37536</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>89009 8 DE OCTUBRE</t>
+          <t>88330 SANTISIMA CRUZ DE MAYO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-9.06422</t>
+          <t>-8.802923</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-78.5858</t>
+          <t>-78.552689</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>462</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>531438</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>89011 ELIAS AGUIRRE ROMERO</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-9.071</t>
+          <t>-9.074117</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-78.58449</t>
+          <t>-78.603457</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>389</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>34533</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>INMACULADA DE LA MERCED</t>
+          <t>88226 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-9.06845</t>
+          <t>-9.07542</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-78.59415</t>
+          <t>-78.57869</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>547</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>34707</t>
+          <t>37503</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>88319 SANTA ROSA DE LIMA PATRONA DE AMERICA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-9.081843</t>
+          <t>-8.967765</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-78.582451</t>
+          <t>-78.583114</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>381</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>34712</t>
+          <t>34873</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>VICTOR ANDRES BELAUNDE</t>
+          <t>SAN JOSE OBRERO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-9.0714</t>
+          <t>-9.05839</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-78.59572</t>
+          <t>-78.58659</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>515</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>34726</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SANTA MARIA REINA</t>
+          <t>88001</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-9.0691</t>
+          <t>-9.07415</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-78.58308</t>
+          <t>-78.59419</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>728</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>34769</t>
+          <t>34298</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>88015 EDITH WEED DAVIS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-9.09775</t>
+          <t>-9.07537</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-78.57054</t>
+          <t>-78.57189</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>516</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>34670</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MICAELA BASTIDAS</t>
+          <t>89009 8 DE OCTUBRE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-9.05796</t>
+          <t>-9.06422</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-78.57932</t>
+          <t>-78.5858</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>403</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>34806</t>
+          <t>35194</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>POLITECNICO NACIONAL DEL SANTA</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-9.0806</t>
+          <t>-9.073782</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-78.58156</t>
+          <t>-78.601514</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>645</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>34873</t>
+          <t>34769</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SAN JOSE OBRERO</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-9.05839</t>
+          <t>-9.09775</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-78.58659</t>
+          <t>-78.57054</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>322</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>35028</t>
+          <t>34302</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>EL SANTA</t>
+          <t>88016 JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-9.073365</t>
+          <t>-9.06955</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-78.590283</t>
+          <t>-78.5768</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>603</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>35170</t>
+          <t>34547</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SAN VICENTE DE PAUL</t>
+          <t>88229 SAN JUAN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-9.07277</t>
+          <t>-9.08813</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-78.59221</t>
+          <t>-78.56885</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>752</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>35194</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>88331</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-9.073782</t>
+          <t>-8.894956000000002</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-78.601514</t>
+          <t>-78.565974</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>622</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>34651</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>VIRGEN DE GUADALUPE</t>
+          <t>89007</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-9.07366</t>
+          <t>-9.06772</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-78.59421</t>
+          <t>-78.58247</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>829</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>35250</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 16</t>
+          <t>EL GRAN MAESTRO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-9.09236</t>
+          <t>-9.11788</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-78.56034</t>
+          <t>-78.52169</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>926</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>35269</t>
+          <t>34383</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NIÑO DIOS</t>
+          <t>88031 REPUBLICA PERUANA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-9.06499</t>
+          <t>-9.06004</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-78.58446</t>
+          <t>-78.58588</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>514</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>35274</t>
+          <t>34590</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ANTONIO RAIMONDI</t>
+          <t>88357 TERESA GONZALES DE FANNING</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-9.07314</t>
+          <t>-9.04638</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-78.59392</t>
+          <t>-78.58619</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>813</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>35957</t>
+          <t>34613</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>88050</t>
+          <t>89001</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-9.014076</t>
+          <t>-9.07225</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-78.138646</t>
+          <t>-78.59539</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>36315</t>
+          <t>34726</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>89506 EDUARDO FERRICK RING</t>
+          <t>SANTA MARIA REINA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-9.022762</t>
+          <t>-9.0691</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-78.619569</t>
+          <t>-78.58308</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>628</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>37051</t>
+          <t>35274</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>88099</t>
+          <t>ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-9.156067</t>
+          <t>-9.07314</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-78.327754</t>
+          <t>-78.59392</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>668</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>34279</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>88049</t>
+          <t>88013 ELEAZAR GUZMAN BARRON</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-8.908032</t>
+          <t>-9.07398</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-78.528023</t>
+          <t>-78.57539</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>687</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>34458</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>88319 SANTA ROSA DE LIMA PATRONA DE AMERICA</t>
+          <t>88046 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-8.967765</t>
+          <t>-8.997156</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-78.583114</t>
+          <t>-78.555489</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>799</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>37536</t>
+          <t>34415</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>88330 SANTISIMA CRUZ DE MAYO</t>
+          <t>88036 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-8.802923</t>
+          <t>-9.05161</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-78.552689</t>
+          <t>-78.58521</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>936</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>37541</t>
+          <t>34806</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>88331</t>
+          <t>POLITECNICO NACIONAL DEL SANTA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-8.894956000000002</t>
+          <t>-9.0806</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-78.565974</t>
+          <t>-78.58156</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>446</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>37918</t>
+          <t>34707</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>88218</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-9.050538</t>
+          <t>-9.081843</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-78.521027</t>
+          <t>-78.582451</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>871</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>34217</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>REAL PACIFICO</t>
+          <t>88005 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-9.127022</t>
+          <t>-9.07792</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-78.524073</t>
+          <t>-78.58883</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>35269</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>EL GRAN MAESTRO</t>
+          <t>NIÑO DIOS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-9.11788</t>
+          <t>-9.06499</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-78.52169</t>
+          <t>-78.58446</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>508193</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SAN FELIPE</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-9.151522</t>
+          <t>-8.908032</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-78.279124</t>
+          <t>-78.528023</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>902</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>530453</t>
+          <t>34420</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MIS PRIMERAS HUELLITAS</t>
+          <t>88037 ANTENOR SANCHEZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-9.06523</t>
+          <t>-9.05295</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-78.58508</t>
+          <t>-78.57464</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>531438</t>
+          <t>34284</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>88014 JOSE OLAYA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-9.074117</t>
+          <t>-9.08523</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-78.603457</t>
+          <t>-78.56895</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>910</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>627389</t>
+          <t>34712</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>EL SANTA</t>
+          <t>VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-9.07548</t>
+          <t>-9.0714</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-78.595441</t>
+          <t>-78.59572</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>851</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>637091</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>VIRGEN DE GUADALUPE</t>
+          <t>FE Y ALEGRIA 16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-9.07354</t>
+          <t>-9.09236</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-78.59463</t>
+          <t>-78.56034</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>706089</t>
+          <t>34627</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BERESHIT</t>
+          <t>89002</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-9.093831</t>
+          <t>-9.07322</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-78.554814</t>
+          <t>-78.59575</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>864248</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>HUMBOLDT KOLLEGIUM</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-9.081713</t>
+          <t>-9.07327</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-78.57332</t>
+          <t>-78.57636</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">

--- a/ZonasEscolares/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/ZonasEscolares/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -3425,7 +3425,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-8.894956000000002</t>
+          <t>-8.894956</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">

--- a/ZonasEscolares/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/ZonasEscolares/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33821</t>
+          <t>864248</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>HUMBOLDT KOLLEGIUM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-9.09037</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.5685</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-9.081713</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.57332</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33939</t>
+          <t>706089</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1535 LA HUACA TESORO DE LOS NIÑOS</t>
+          <t>BERESHIT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.051293</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.587742</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-9.093831</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.554814</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>35170</t>
+          <t>637091</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SAN VICENTE DE PAUL</t>
+          <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.07277</t>
+          <t>401</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.59221</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-9.07354</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.59463</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34496</t>
+          <t>627389</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>88072</t>
+          <t>EL SANTA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.05615</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.57751</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-9.07548</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-78.595441</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>531438</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>INMACULADA DE LA MERCED</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.06845</t>
+          <t>389</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.59415</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>-9.074117</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>-78.603457</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33840</t>
+          <t>530453</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>316 NIÑO JESUS</t>
+          <t>MIS PRIMERAS HUELLITAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.07039</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.59414</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-9.06523</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-78.58508</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>508193</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>88239 LEONCIO PRADO</t>
+          <t>SAN FELIPE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.08119</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.57252</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>-9.151522</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.279124</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33963</t>
+          <t>038526</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1542 CAPULLITOS DE AMOR</t>
+          <t>EL GRAN MAESTRO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.05762</t>
+          <t>926</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.58641</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>-9.11788</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.52169</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37051</t>
+          <t>038418</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>88099</t>
+          <t>REAL PACIFICO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9.156067</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.327754</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-9.127022</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.524073</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34514</t>
+          <t>037918</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>88183</t>
+          <t>88218</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.946399</t>
+          <t>241</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.517631</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>-9.050538</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-78.521027</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37918</t>
+          <t>037541</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>88218</t>
+          <t>88331</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.050538</t>
+          <t>622</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.521027</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>-8.894956000000002</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-78.565974</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>637091</t>
+          <t>037536</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VIRGEN DE GUADALUPE</t>
+          <t>88330 SANTISIMA CRUZ DE MAYO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.07354</t>
+          <t>462</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.59463</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>-8.802923</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-78.552689</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>530453</t>
+          <t>037503</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIS PRIMERAS HUELLITAS</t>
+          <t>88319 SANTA ROSA DE LIMA PATRONA DE AMERICA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.06523</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.58508</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-8.967765</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.583114</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>34104</t>
+          <t>037367</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>89013</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-9.07191</t>
+          <t>902</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-78.58342</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-8.908032</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.528023</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>34222</t>
+          <t>037051</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>88008 MANUEL PERALTA HURTADO</t>
+          <t>88099</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-9.0889</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-78.57471</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>-9.156067</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.327754</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>34260</t>
+          <t>036315</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>88012</t>
+          <t>89506 EDUARDO FERRICK RING</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-9.07921</t>
+          <t>568</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.57726</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-9.022762</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.619569</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>035957</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VIRGEN DE GUADALUPE</t>
+          <t>88050</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-9.07366</t>
+          <t>292</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.59421</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>-9.014076</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.138646</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>34255</t>
+          <t>035274</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>88011 INCA GARCILASO DE LA VEGA</t>
+          <t>ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.103114</t>
+          <t>668</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.565121</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-9.07314</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-78.59392</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35028</t>
+          <t>035269</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EL SANTA</t>
+          <t>NIÑO DIOS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-9.073365</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-78.590283</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-9.06499</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-78.58446</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>035250</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>REAL PACIFICO</t>
+          <t>FE Y ALEGRIA 16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-9.127022</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.524073</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>-9.09236</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-78.56034</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>508193</t>
+          <t>035245</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAN FELIPE</t>
+          <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-9.151522</t>
+          <t>431</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-78.279124</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-9.07366</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-78.59421</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>864248</t>
+          <t>035194</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HUMBOLDT KOLLEGIUM</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-9.081713</t>
+          <t>645</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.57332</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-9.073782</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-78.601514</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>33802</t>
+          <t>035170</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>302 RUSO</t>
+          <t>SAN VICENTE DE PAUL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-9.07639</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.58864</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-9.07277</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.59221</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34397</t>
+          <t>035028</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>88032 APOSTOL SAN PEDRO</t>
+          <t>EL SANTA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-9.045787</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-78.591611</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>-9.073365</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.590283</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>034873</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>89011 ELIAS AGUIRRE ROMERO</t>
+          <t>SAN JOSE OBRERO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.071</t>
+          <t>515</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-78.58449</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>-9.05839</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-78.58659</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>627389</t>
+          <t>034806</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>EL SANTA</t>
+          <t>POLITECNICO NACIONAL DEL SANTA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-9.07548</t>
+          <t>446</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-78.595441</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-9.0806</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-78.58156</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>034788</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>88009 ENRIQUE MEIGGS</t>
+          <t>MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-9.09325</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-78.5699</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>-9.05796</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-78.57932</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>35957</t>
+          <t>034769</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>88050</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-9.014076</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.138646</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>-9.09775</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-78.57054</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>34062</t>
+          <t>034726</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>88232 NUESTRA VIRGEN MARIA</t>
+          <t>SANTA MARIA REINA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-9.0774</t>
+          <t>628</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.58079</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>-9.0691</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-78.58308</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>034712</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>88020 VIRGEN DEL CARMEN</t>
+          <t>VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-9.06101</t>
+          <t>851</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.58129</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>-9.0714</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-78.59572</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>34665</t>
+          <t>034707</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>89008 ANDRES AVELINO CACERES</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-9.05274</t>
+          <t>871</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.582008</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>-9.081843</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-78.582451</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>706089</t>
+          <t>034694</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BERESHIT</t>
+          <t>INMACULADA DE LA MERCED</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-9.093831</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-78.554814</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-9.06845</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-78.59415</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>34401</t>
+          <t>034689</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>88034 PEDRO RUIZ GALLO</t>
+          <t>89011 ELIAS AGUIRRE ROMERO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-9.05797</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-78.58932</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>-9.071</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-78.58449</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>034670</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MICAELA BASTIDAS</t>
+          <t>89009 8 DE OCTUBRE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-9.05796</t>
+          <t>403</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-78.57932</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>-9.06422</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-78.5858</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>36315</t>
+          <t>034665</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>89506 EDUARDO FERRICK RING</t>
+          <t>89008 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-9.022762</t>
+          <t>415</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-78.619569</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>-9.05274</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-78.582008</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>37536</t>
+          <t>034651</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>88330 SANTISIMA CRUZ DE MAYO</t>
+          <t>89007</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.802923</t>
+          <t>829</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-78.552689</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>-9.06772</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-78.58247</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>531438</t>
+          <t>034627</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>89002</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-9.074117</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-78.603457</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>-9.07322</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-78.59575</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>34533</t>
+          <t>034613</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>88226 DANIEL ALCIDES CARRION</t>
+          <t>89001</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-9.07542</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-78.57869</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>-9.07225</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-78.59539</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>034590</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>88319 SANTA ROSA DE LIMA PATRONA DE AMERICA</t>
+          <t>88357 TERESA GONZALES DE FANNING</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8.967765</t>
+          <t>813</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-78.583114</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>-9.04638</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-78.58619</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>34873</t>
+          <t>034552</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SAN JOSE OBRERO</t>
+          <t>88239 LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-9.05839</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-78.58659</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>-9.08119</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-78.57252</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>034547</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>88001</t>
+          <t>88229 SAN JUAN</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-9.07415</t>
+          <t>752</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-78.59419</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>-9.08813</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-78.56885</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>34298</t>
+          <t>034533</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>88015 EDITH WEED DAVIS</t>
+          <t>88226 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-9.07537</t>
+          <t>547</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-78.57189</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>-9.07542</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-78.57869</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>034514</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>89009 8 DE OCTUBRE</t>
+          <t>88183</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-9.06422</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-78.5858</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>-8.946399</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-78.517631</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>35194</t>
+          <t>034496</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>88072</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-9.073782</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-78.601514</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>-9.05615</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-78.57751</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>34769</t>
+          <t>034458</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>88046 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-9.09775</t>
+          <t>799</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-78.57054</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>-8.997156</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-78.555489</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>34302</t>
+          <t>034420</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>88016 JOSE GALVEZ EGUSQUIZA</t>
+          <t>88037 ANTENOR SANCHEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-9.06955</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-78.5768</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>-9.05295</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-78.57464</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>34547</t>
+          <t>034415</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>88229 SAN JUAN</t>
+          <t>88036 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-9.08813</t>
+          <t>936</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-78.56885</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>-9.05161</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-78.58521</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>37541</t>
+          <t>034401</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>88331</t>
+          <t>88034 PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-8.894956</t>
+          <t>582</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-78.565974</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>-9.05797</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-78.58932</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>34651</t>
+          <t>034397</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>89007</t>
+          <t>88032 APOSTOL SAN PEDRO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-9.06772</t>
+          <t>402</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-78.58247</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>-9.045787</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-78.591611</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>034383</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>EL GRAN MAESTRO</t>
+          <t>88031 REPUBLICA PERUANA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-9.11788</t>
+          <t>514</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-78.52169</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>-9.06004</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-78.58588</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>34383</t>
+          <t>034335</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>88031 REPUBLICA PERUANA</t>
+          <t>88020 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-9.06004</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-78.58588</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>-9.06101</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-78.58129</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>34590</t>
+          <t>034302</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>88357 TERESA GONZALES DE FANNING</t>
+          <t>88016 JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-9.04638</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-78.58619</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>-9.06955</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-78.5768</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>34613</t>
+          <t>034298</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>89001</t>
+          <t>88015 EDITH WEED DAVIS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-9.07225</t>
+          <t>516</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-78.59539</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>-9.07537</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-78.57189</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>34726</t>
+          <t>034284</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SANTA MARIA REINA</t>
+          <t>88014 JOSE OLAYA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-9.0691</t>
+          <t>910</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-78.58308</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>-9.08523</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-78.56895</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>35274</t>
+          <t>034279</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ANTONIO RAIMONDI</t>
+          <t>88013 ELEAZAR GUZMAN BARRON</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-9.07314</t>
+          <t>687</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-78.59392</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>-9.07398</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-78.57539</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>34279</t>
+          <t>034260</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>88013 ELEAZAR GUZMAN BARRON</t>
+          <t>88012</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-9.07398</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-78.57539</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>-9.07921</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-78.57726</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>34458</t>
+          <t>034255</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>88046 JOSE CARLOS MARIATEGUI</t>
+          <t>88011 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-8.997156</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-78.555489</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>-9.103114</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-78.565121</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>34415</t>
+          <t>034236</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>88036 MARIANO MELGAR</t>
+          <t>88009 ENRIQUE MEIGGS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-9.05161</t>
+          <t>537</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-78.58521</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>-9.09325</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-78.5699</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>34806</t>
+          <t>034222</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>POLITECNICO NACIONAL DEL SANTA</t>
+          <t>88008 MANUEL PERALTA HURTADO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-9.0806</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-78.58156</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>-9.0889</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-78.57471</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>34707</t>
+          <t>034217</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>88005 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-9.081843</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-78.582451</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>-9.07792</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-78.58883</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>34217</t>
+          <t>034180</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>88005 CORAZON DE JESUS</t>
+          <t>88001</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-9.07792</t>
+          <t>728</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-78.58883</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>-9.07415</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-78.59419</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>35269</t>
+          <t>034104</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NIÑO DIOS</t>
+          <t>89013</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-9.06499</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-78.58446</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>-9.07191</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-78.58342</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>034062</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>88049</t>
+          <t>88232 NUESTRA VIRGEN MARIA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-8.908032</t>
+          <t>519</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-78.528023</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>-9.0774</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-78.58079</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>34420</t>
+          <t>034000</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>88037 ANTENOR SANCHEZ</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-9.05295</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-78.57464</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>-9.07327</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-78.57636</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>34284</t>
+          <t>033963</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>88014 JOSE OLAYA</t>
+          <t>1542 CAPULLITOS DE AMOR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-9.08523</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-78.56895</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>-9.05762</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-78.58641</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>34712</t>
+          <t>033939</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>VICTOR ANDRES BELAUNDE</t>
+          <t>1535 LA HUACA TESORO DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-9.0714</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-78.59572</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>-9.051293</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-78.587742</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>35250</t>
+          <t>033840</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 16</t>
+          <t>316 NIÑO JESUS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-9.09236</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-78.56034</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>-9.07039</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-78.59414</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>34627</t>
+          <t>033821</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>89002</t>
+          <t>313</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-9.07322</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-78.59575</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>-9.09037</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>-78.5685</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>033802</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>302 RUSO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-9.07327</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-78.57636</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-9.07639</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-78.58864</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">

--- a/ZonasEscolares/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/ZonasEscolares/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
